--- a/examples/excel/charts/charts-line.xlsx
+++ b/examples/excel/charts/charts-line.xlsx
@@ -3,14 +3,14 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Line Fundamentals" sheetId="2" r:id="R6c8d488a8f9d4033"/>
-    <x:sheet name="2-Line Styles" sheetId="3" r:id="R4c99dd598bc6496c"/>
-    <x:sheet name="3-Line Variants" sheetId="4" r:id="R486ebd1dd09b4660"/>
-    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R0f79507c2e5944e4"/>
-    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="Rc5029a96510a4ff4"/>
-    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="Rdb7425d8efc94a73"/>
-    <x:sheet name="7-Line Elements" sheetId="8" r:id="Rb4283abf8c1244bb"/>
-    <x:sheet name="8-Axis Extras" sheetId="9" r:id="R0dd09002bb794612"/>
+    <x:sheet name="1-Line Fundamentals" sheetId="2" r:id="Rf084f691f4c9437a"/>
+    <x:sheet name="2-Line Styles" sheetId="3" r:id="R43b24d1bc0164b1b"/>
+    <x:sheet name="3-Line Variants" sheetId="4" r:id="R651bfd14cbdd43de"/>
+    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R7a676d49c2c74399"/>
+    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="Ra5ce7a1101084642"/>
+    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="Rf9cc3737637648b0"/>
+    <x:sheet name="7-Line Elements" sheetId="8" r:id="R00c36a9350b140f6"/>
+    <x:sheet name="8-Axis Extras" sheetId="9" r:id="R0afdb4d4ae324b27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,9 +92,11 @@
             <c:v>Product A</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -139,9 +141,11 @@
             <c:v>Product B</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -186,9 +190,11 @@
             <c:v>Product C</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -380,9 +386,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -481,9 +489,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -582,9 +592,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9DC3E6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -683,9 +695,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="BDD7EE"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="BDD7EE"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -871,9 +885,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -972,9 +988,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1073,9 +1091,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1174,9 +1194,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1362,10 +1384,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1464,10 +1487,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1566,10 +1590,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1668,10 +1693,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1849,9 +1875,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1959,9 +1987,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2069,9 +2099,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2179,9 +2211,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -2400,10 +2434,11 @@
             <c:v>Growth</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="triangle"/>
@@ -2588,10 +2623,11 @@
             <c:v>Depth</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -2759,10 +2795,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="star"/>
@@ -2828,10 +2865,11 @@
             <c:v>Cost</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="star"/>
@@ -3010,10 +3048,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -3169,10 +3208,11 @@
             <c:v>Sales</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -3369,10 +3409,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -3471,10 +3512,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -3573,10 +3615,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -3675,10 +3718,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -3869,9 +3913,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -3885,11 +3931,90 @@
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>198</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4013,10 +4138,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -4115,10 +4241,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -4217,10 +4344,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -4319,10 +4447,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -4503,10 +4632,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -4587,10 +4717,11 @@
             <c:v>Growth %</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -4802,10 +4933,10 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
               <a:prstDash val="lgDash"/>
             </a:ln>
           </c:spPr>
@@ -4915,10 +5046,10 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
               <a:prstDash val="lgDash"/>
             </a:ln>
           </c:spPr>
@@ -5185,10 +5316,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="38100" dist="12700" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -5253,10 +5385,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="38100" dist="12700" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -5404,10 +5537,11 @@
             <c:v>Profit</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -5741,9 +5875,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -5851,9 +5987,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -6035,9 +6173,11 @@
             <c:v>High</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -6103,9 +6243,11 @@
             <c:v>Low</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -6245,9 +6387,11 @@
             <c:v>Open</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -6313,9 +6457,11 @@
             <c:v>Close</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -6476,9 +6622,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -6577,9 +6725,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -6678,9 +6828,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -6779,9 +6931,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -6968,10 +7122,11 @@
             <c:v>Score</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -7110,10 +7265,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -7221,10 +7377,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -7332,10 +7489,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -7443,10 +7601,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -7642,10 +7801,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="548235"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -7772,10 +7932,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -7902,10 +8063,11 @@
             <c:v>Index</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="7030A0"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -8040,18 +8202,32 @@
             <c:v>Actual</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
+              <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>Week</c:v>
+                <c:v>Week 1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Week 2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Week 3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Week 4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Week 5</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -8084,18 +8260,32 @@
             <c:v>Target</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
+              <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>Week</c:v>
+                <c:v>Week 1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Week 2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Week 3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Week 4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Week 5</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -8200,10 +8390,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -8310,10 +8501,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="00B050"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -8420,10 +8612,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -8530,10 +8723,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -8712,10 +8906,10 @@
             <c:v>solid</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -8768,10 +8962,10 @@
             <c:v>dot</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -8824,10 +9018,10 @@
             <c:v>dash</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -8880,10 +9074,10 @@
             <c:v>dashdot</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -9008,9 +9202,6 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -9123,9 +9314,6 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -9238,9 +9426,6 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -9353,9 +9538,6 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
                 <a:srgbClr val="FFFFFF"/>
@@ -9548,12 +9730,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1F4E79">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -9653,12 +9834,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -9758,12 +9938,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="5B9BD5">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="5B9BD5"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -9863,12 +10042,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9DC3E6">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -10059,9 +10237,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -10160,9 +10340,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -10261,9 +10443,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -10362,9 +10546,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -10564,7 +10750,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c7aaf7bbe484f09"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfc2afd138fce427b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10594,7 +10780,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bb1ee656e004c3a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5827208cf0a446d2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10624,7 +10810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redb9511d7c0e4d9d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree79b056407242fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10654,7 +10840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R455cea3f2e194acf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R379d3f0ad5604850"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10689,7 +10875,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1686326314ab4db1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3d6242b3a4ea457d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10719,7 +10905,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0e48c25aab4462a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb674fdf2b5a4174"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10749,7 +10935,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf24858f4e37a4dc8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd796512112844d9c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10779,7 +10965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra23aac3af724432e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9cd3ff57033646aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10814,7 +11000,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b2d5f8be3b54c66"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8c20e1642ea492d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10844,7 +11030,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf455eebaaa94452c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Race2f993987b4f8d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10874,7 +11060,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ad2a55a1565498f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re4c1567f2ee04fc3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10904,7 +11090,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8729128951c4cd3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb9f6ea06bf8499c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10939,7 +11125,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R585fa3ff8b544bb7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R80c3f3a70d4549f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10969,7 +11155,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29304db882e14bc3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7dff6f6889194879"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10999,7 +11185,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbcaa9aaf4f0f4c65"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red5df6cc7dbc4cea"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11029,7 +11215,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1fb8439c729a476d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaed762a85ec4e0a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11064,7 +11250,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7de0420ecdfb4022"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb7283524ff454c12"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11094,7 +11280,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf7e55804fefa43b4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29368815d624426f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11124,7 +11310,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95ea5694838a49ad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf32df2e3df0c4789"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11154,7 +11340,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33b7f4eccaf248b9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51ec8627bc114272"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11189,7 +11375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd852874e74744ecb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R073ea7ed7dc34d3f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11219,7 +11405,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38213bb896364678"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c4948ec9a6d45e8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11249,7 +11435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfd6cb014878c47d1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30658c8430144176"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11279,7 +11465,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95f49e074c2e4b11"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R009264d5adda4a93"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11314,7 +11500,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re1db44f913b9435c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re1ba25c7f5f943f3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11344,7 +11530,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a0f9e739194d33"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc9566c9e6434a93"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11374,7 +11560,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3602d8b741f243c2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R11dcccc128164f13"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11404,7 +11590,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c6f44e29c9b4f9c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R07db897e6f0c4531"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11439,7 +11625,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb46d973c4e5d4707"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfa4d3473d1b9486a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11469,7 +11655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78b9c98ba75c4f2e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00a340d79ebd4fd0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11499,7 +11685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redc1cefc97eb4b48"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R09ea8f1c18af4fe9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11529,13 +11715,122 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29fc3da1b0a2446b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R823813a51cf94384"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11769,55 +12064,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f8947c654374516"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e082f5788a4f2d"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca9d551801e46d7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc231f7ed155c44ed"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf14950f47f34265"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a45b9460648401e"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9632bdbe854730"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64b3c61fc7754142"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd22d1ebf2d40f9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0edf43597c6d41c6"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba965dc4e91e4909"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893b886bbacd4060"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5661d60d16f04bb9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R587f3a7e42994625"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cb0f41c87b84584"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2d22a1e93bb4a29"/>
 </x:worksheet>
 </file>